--- a/prodotti.xlsx
+++ b/prodotti.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\flashmac\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{19057DBE-1980-4638-AFB1-08A8F4FFA8AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{132AFE54-BD9F-4D0A-B461-1CEC30A16C8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1905" yWindow="1905" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Attivi" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="170">
   <si>
     <t>prodotto</t>
   </si>
@@ -103,9 +103,6 @@
   </si>
   <si>
     <t>Rinnova Valore Bonus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prodotto </t>
   </si>
   <si>
     <t>02mg  standard</t>
@@ -1022,7 +1019,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
@@ -1030,7 +1027,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B2" t="s">
         <v>10</v>
@@ -1038,7 +1035,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B3" t="s">
         <v>10</v>
@@ -1046,7 +1043,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B4" t="s">
         <v>10</v>
@@ -1054,15 +1051,15 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B6" t="s">
         <v>10</v>
@@ -1070,7 +1067,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B7" t="s">
         <v>10</v>
@@ -1078,7 +1075,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B8" t="s">
         <v>10</v>
@@ -1086,7 +1083,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B9" t="s">
         <v>10</v>
@@ -1094,7 +1091,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B10" t="s">
         <v>10</v>
@@ -1102,7 +1099,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B11" t="s">
         <v>10</v>
@@ -1110,7 +1107,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B12" t="s">
         <v>10</v>
@@ -1118,7 +1115,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B13" t="s">
         <v>10</v>
@@ -1126,7 +1123,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B14" t="s">
         <v>10</v>
@@ -1134,7 +1131,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B15" t="s">
         <v>10</v>
@@ -1142,7 +1139,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B16" t="s">
         <v>10</v>
@@ -1150,7 +1147,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B17" t="s">
         <v>10</v>
@@ -1158,7 +1155,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B18" t="s">
         <v>10</v>
@@ -1166,7 +1163,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B19" t="s">
         <v>10</v>
@@ -1174,7 +1171,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B20" t="s">
         <v>10</v>
@@ -1182,7 +1179,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B21" t="s">
         <v>10</v>
@@ -1190,7 +1187,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B22" t="s">
         <v>10</v>
@@ -1198,7 +1195,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B23" t="s">
         <v>10</v>
@@ -1206,7 +1203,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B24" t="s">
         <v>10</v>
@@ -1214,7 +1211,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B25" t="s">
         <v>10</v>
@@ -1222,7 +1219,7 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B26" t="s">
         <v>10</v>
@@ -1230,7 +1227,7 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B27" t="s">
         <v>10</v>
@@ -1238,7 +1235,7 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B28" t="s">
         <v>10</v>
@@ -1246,7 +1243,7 @@
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B29" t="s">
         <v>10</v>
@@ -1254,7 +1251,7 @@
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B30" t="s">
         <v>10</v>
@@ -1262,7 +1259,7 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B31" t="s">
         <v>10</v>
@@ -1270,7 +1267,7 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B32" t="s">
         <v>10</v>
@@ -1278,7 +1275,7 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B33" t="s">
         <v>10</v>
@@ -1286,7 +1283,7 @@
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B34" t="s">
         <v>10</v>
@@ -1294,7 +1291,7 @@
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B35" t="s">
         <v>13</v>
@@ -1302,7 +1299,7 @@
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B36" t="s">
         <v>13</v>
@@ -1310,7 +1307,7 @@
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B37" t="s">
         <v>13</v>
@@ -1318,7 +1315,7 @@
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B38" t="s">
         <v>13</v>
@@ -1326,7 +1323,7 @@
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B39" t="s">
         <v>13</v>
@@ -1334,7 +1331,7 @@
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B40" t="s">
         <v>13</v>
@@ -1342,39 +1339,39 @@
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B41" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B42" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B43" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B44" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B45" t="s">
         <v>10</v>
@@ -1382,39 +1379,39 @@
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B46" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B47" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B48" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B49" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B50" t="s">
         <v>10</v>
@@ -1422,15 +1419,15 @@
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B51" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B52" t="s">
         <v>10</v>
@@ -1438,7 +1435,7 @@
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B53" t="s">
         <v>10</v>
@@ -1446,39 +1443,39 @@
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B54" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B55" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B56" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B57" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B58" t="s">
         <v>10</v>
@@ -1486,7 +1483,7 @@
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B59" t="s">
         <v>10</v>
@@ -1494,7 +1491,7 @@
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B60" t="s">
         <v>10</v>
@@ -1502,7 +1499,7 @@
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B61" t="s">
         <v>3</v>
@@ -1510,7 +1507,7 @@
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B62" t="s">
         <v>10</v>
@@ -1518,7 +1515,7 @@
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B63" t="s">
         <v>10</v>
@@ -1526,7 +1523,7 @@
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B64" t="s">
         <v>3</v>
@@ -1534,7 +1531,7 @@
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B65" t="s">
         <v>10</v>
@@ -1542,7 +1539,7 @@
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B66" t="s">
         <v>10</v>
@@ -1550,7 +1547,7 @@
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B67" t="s">
         <v>10</v>
@@ -1558,7 +1555,7 @@
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B68" t="s">
         <v>10</v>
@@ -1566,7 +1563,7 @@
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B69" t="s">
         <v>3</v>
@@ -1574,7 +1571,7 @@
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B70" t="s">
         <v>3</v>
@@ -1582,7 +1579,7 @@
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B71" t="s">
         <v>3</v>
@@ -1590,15 +1587,15 @@
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B72" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B73" t="s">
         <v>10</v>
@@ -1606,7 +1603,7 @@
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B74" t="s">
         <v>10</v>
@@ -1614,7 +1611,7 @@
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B75" t="s">
         <v>10</v>
@@ -1622,7 +1619,7 @@
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B76" t="s">
         <v>10</v>
@@ -1630,7 +1627,7 @@
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B77" t="s">
         <v>10</v>
@@ -1638,7 +1635,7 @@
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B78" t="s">
         <v>10</v>
@@ -1646,7 +1643,7 @@
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B79" t="s">
         <v>10</v>
@@ -1654,7 +1651,7 @@
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B80" t="s">
         <v>13</v>
@@ -1662,15 +1659,15 @@
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B81" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B82" t="s">
         <v>13</v>
@@ -1678,7 +1675,7 @@
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B83" t="s">
         <v>10</v>
@@ -1686,7 +1683,7 @@
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B84" t="s">
         <v>10</v>
@@ -1694,7 +1691,7 @@
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B85" t="s">
         <v>10</v>
@@ -1702,7 +1699,7 @@
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B86" t="s">
         <v>10</v>
@@ -1710,7 +1707,7 @@
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B87" t="s">
         <v>10</v>
@@ -1718,95 +1715,95 @@
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B88" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B89" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B90" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B91" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B92" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B93" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B94" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B95" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B96" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B97" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B98" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B99" t="s">
         <v>10</v>
@@ -1814,7 +1811,7 @@
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B100" t="s">
         <v>10</v>
@@ -1822,7 +1819,7 @@
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B101" t="s">
         <v>10</v>
@@ -1830,7 +1827,7 @@
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B102" t="s">
         <v>10</v>
@@ -1838,7 +1835,7 @@
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B103" t="s">
         <v>10</v>
@@ -1846,7 +1843,7 @@
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B104" t="s">
         <v>10</v>
@@ -1854,7 +1851,7 @@
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B105" t="s">
         <v>10</v>
@@ -1862,7 +1859,7 @@
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B106" t="s">
         <v>10</v>
@@ -1870,7 +1867,7 @@
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B107" t="s">
         <v>13</v>
@@ -1878,7 +1875,7 @@
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B108" t="s">
         <v>10</v>
@@ -1886,7 +1883,7 @@
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B109" t="s">
         <v>10</v>
@@ -1894,39 +1891,39 @@
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B110" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B111" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B112" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B113" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B114" t="s">
         <v>3</v>
@@ -1934,7 +1931,7 @@
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B115" t="s">
         <v>10</v>
@@ -1942,7 +1939,7 @@
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B116" t="s">
         <v>10</v>
@@ -1950,31 +1947,31 @@
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B117" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B118" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B119" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B120" t="s">
         <v>13</v>
@@ -1982,7 +1979,7 @@
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B121" t="s">
         <v>13</v>
@@ -1990,7 +1987,7 @@
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B122" t="s">
         <v>13</v>
@@ -1998,7 +1995,7 @@
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B123" t="s">
         <v>13</v>
@@ -2006,7 +2003,7 @@
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B124" t="s">
         <v>13</v>
@@ -2014,7 +2011,7 @@
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B125" t="s">
         <v>13</v>
@@ -2022,15 +2019,15 @@
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B126" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B127" t="s">
         <v>13</v>
@@ -2038,7 +2035,7 @@
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B128" t="s">
         <v>10</v>
@@ -2046,31 +2043,31 @@
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B129" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B130" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B131" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B132" t="s">
         <v>13</v>
@@ -2078,7 +2075,7 @@
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B133" t="s">
         <v>13</v>
@@ -2086,7 +2083,7 @@
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B134" t="s">
         <v>13</v>
@@ -2094,7 +2091,7 @@
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B135" t="s">
         <v>10</v>
@@ -2102,7 +2099,7 @@
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B136" t="s">
         <v>10</v>
@@ -2110,7 +2107,7 @@
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B137" t="s">
         <v>10</v>
@@ -2118,7 +2115,7 @@
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B138" t="s">
         <v>10</v>
@@ -2126,15 +2123,15 @@
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B139" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B140" t="s">
         <v>10</v>
@@ -2142,7 +2139,7 @@
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B141" t="s">
         <v>3</v>
@@ -2150,7 +2147,7 @@
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B142" t="s">
         <v>10</v>
@@ -2158,47 +2155,47 @@
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B143" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B144" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B145" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B146" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B147" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B148" t="s">
         <v>10</v>
@@ -2206,7 +2203,7 @@
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B149" t="s">
         <v>10</v>

--- a/prodotti.xlsx
+++ b/prodotti.xlsx
@@ -8,14 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\flashmac\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{132AFE54-BD9F-4D0A-B461-1CEC30A16C8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB410E43-0D82-4C0D-9E91-16557F1D947C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1905" yWindow="1905" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Attivi" sheetId="1" r:id="rId1"/>
     <sheet name="PTF" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Attivi!$A$1:$C$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">PTF!$A$1:$C$149</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -40,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="495" uniqueCount="174">
   <si>
     <t>prodotto</t>
   </si>
@@ -550,6 +554,18 @@
   </si>
   <si>
     <t>Valore protetto new</t>
+  </si>
+  <si>
+    <t>componente</t>
+  </si>
+  <si>
+    <t>PU</t>
+  </si>
+  <si>
+    <t>PA</t>
+  </si>
+  <si>
+    <t>PA + PU</t>
   </si>
 </sst>
 </file>
@@ -868,1348 +884,1845 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C1" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C2" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C3" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>6</v>
       </c>
       <c r="B4" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C4" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C5" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>8</v>
       </c>
       <c r="B6" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C6" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>9</v>
       </c>
       <c r="B7" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C7" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>11</v>
       </c>
       <c r="B8" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C8" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>12</v>
       </c>
       <c r="B9" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C9" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>14</v>
       </c>
       <c r="B10" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C10" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>15</v>
       </c>
       <c r="B11" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C11" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>16</v>
       </c>
       <c r="B12" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C12" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>17</v>
       </c>
       <c r="B13" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C13" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B14" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C14" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>19</v>
       </c>
       <c r="B15" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C15" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>20</v>
       </c>
       <c r="B16" t="s">
         <v>5</v>
       </c>
+      <c r="C16" t="s">
+        <v>171</v>
+      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:C16" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08FC4AC1-13E2-4978-9F20-D861F52E4B90}">
-  <dimension ref="A1:B149"/>
+  <dimension ref="A1:C149"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C1" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>21</v>
       </c>
       <c r="B2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C2" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>22</v>
       </c>
       <c r="B3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C3" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>23</v>
       </c>
       <c r="B4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C4" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>24</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C5" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>26</v>
       </c>
       <c r="B6" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C6" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>27</v>
       </c>
       <c r="B7" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C7" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>28</v>
       </c>
       <c r="B8" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C8" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>29</v>
       </c>
       <c r="B9" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C9" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>30</v>
       </c>
       <c r="B10" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C10" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>31</v>
       </c>
       <c r="B11" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C11" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>32</v>
       </c>
       <c r="B12" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C12" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>33</v>
       </c>
       <c r="B13" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C13" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>34</v>
       </c>
       <c r="B14" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C14" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>35</v>
       </c>
       <c r="B15" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C15" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>36</v>
       </c>
       <c r="B16" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C16" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>37</v>
       </c>
       <c r="B17" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C17" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>38</v>
       </c>
       <c r="B18" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C18" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>39</v>
       </c>
       <c r="B19" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C19" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>40</v>
       </c>
       <c r="B20" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C20" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>41</v>
       </c>
       <c r="B21" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C21" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>42</v>
       </c>
       <c r="B22" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C22" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>43</v>
       </c>
       <c r="B23" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C23" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>44</v>
       </c>
       <c r="B24" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C24" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>45</v>
       </c>
       <c r="B25" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C25" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>46</v>
       </c>
       <c r="B26" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C26" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>47</v>
       </c>
       <c r="B27" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C27" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>48</v>
       </c>
       <c r="B28" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C28" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>49</v>
       </c>
       <c r="B29" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C29" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>50</v>
       </c>
       <c r="B30" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C30" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>51</v>
       </c>
       <c r="B31" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C31" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>52</v>
       </c>
       <c r="B32" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C32" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>53</v>
       </c>
       <c r="B33" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C33" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>54</v>
       </c>
       <c r="B34" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C34" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>55</v>
       </c>
       <c r="B35" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C35" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>56</v>
       </c>
       <c r="B36" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C36" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>57</v>
       </c>
       <c r="B37" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C37" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>58</v>
       </c>
       <c r="B38" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C38" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>59</v>
       </c>
       <c r="B39" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C39" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>60</v>
       </c>
       <c r="B40" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C40" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>61</v>
       </c>
       <c r="B41" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C41" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>62</v>
       </c>
       <c r="B42" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C42" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>63</v>
       </c>
       <c r="B43" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C43" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>64</v>
       </c>
       <c r="B44" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C44" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>65</v>
       </c>
       <c r="B45" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C45" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>66</v>
       </c>
       <c r="B46" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C46" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>67</v>
       </c>
       <c r="B47" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C47" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>68</v>
       </c>
       <c r="B48" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C48" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>69</v>
       </c>
       <c r="B49" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C49" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>70</v>
       </c>
       <c r="B50" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C50" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>71</v>
       </c>
       <c r="B51" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C51" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>72</v>
       </c>
       <c r="B52" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C52" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>73</v>
       </c>
       <c r="B53" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C53" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>74</v>
       </c>
       <c r="B54" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C54" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>75</v>
       </c>
       <c r="B55" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C55" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>76</v>
       </c>
       <c r="B56" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C56" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>77</v>
       </c>
       <c r="B57" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C57" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>78</v>
       </c>
       <c r="B58" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C58" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>79</v>
       </c>
       <c r="B59" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C59" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>80</v>
       </c>
       <c r="B60" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C60" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>81</v>
       </c>
       <c r="B61" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C61" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>82</v>
       </c>
       <c r="B62" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C62" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>83</v>
       </c>
       <c r="B63" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C63" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>84</v>
       </c>
       <c r="B64" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C64" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>85</v>
       </c>
       <c r="B65" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C65" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>86</v>
       </c>
       <c r="B66" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C66" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>87</v>
       </c>
       <c r="B67" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C67" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>88</v>
       </c>
       <c r="B68" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C68" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>89</v>
       </c>
       <c r="B69" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C69" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>90</v>
       </c>
       <c r="B70" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C70" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>91</v>
       </c>
       <c r="B71" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C71" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>92</v>
       </c>
       <c r="B72" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C72" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>93</v>
       </c>
       <c r="B73" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C73" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>94</v>
       </c>
       <c r="B74" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C74" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>95</v>
       </c>
       <c r="B75" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C75" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>96</v>
       </c>
       <c r="B76" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C76" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>97</v>
       </c>
       <c r="B77" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C77" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>98</v>
       </c>
       <c r="B78" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C78" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>99</v>
       </c>
       <c r="B79" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C79" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>100</v>
       </c>
       <c r="B80" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C80" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>101</v>
       </c>
       <c r="B81" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C81" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>102</v>
       </c>
       <c r="B82" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C82" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>103</v>
       </c>
       <c r="B83" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C83" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>104</v>
       </c>
       <c r="B84" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C84" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>105</v>
       </c>
       <c r="B85" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C85" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>106</v>
       </c>
       <c r="B86" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C86" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>107</v>
       </c>
       <c r="B87" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C87" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>108</v>
       </c>
       <c r="B88" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C88" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>109</v>
       </c>
       <c r="B89" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C89" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>110</v>
       </c>
       <c r="B90" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C90" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>111</v>
       </c>
       <c r="B91" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C91" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>112</v>
       </c>
       <c r="B92" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C92" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>113</v>
       </c>
       <c r="B93" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C93" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>114</v>
       </c>
       <c r="B94" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C94" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>115</v>
       </c>
       <c r="B95" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C95" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>116</v>
       </c>
       <c r="B96" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C96" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>117</v>
       </c>
       <c r="B97" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C97" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>118</v>
       </c>
       <c r="B98" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C98" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>119</v>
       </c>
       <c r="B99" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C99" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>120</v>
       </c>
       <c r="B100" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C100" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>121</v>
       </c>
       <c r="B101" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C101" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>122</v>
       </c>
       <c r="B102" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C102" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>123</v>
       </c>
       <c r="B103" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C103" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>124</v>
       </c>
       <c r="B104" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C104" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>125</v>
       </c>
       <c r="B105" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C105" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>126</v>
       </c>
       <c r="B106" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C106" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>127</v>
       </c>
       <c r="B107" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C107" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>128</v>
       </c>
       <c r="B108" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C108" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>129</v>
       </c>
       <c r="B109" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C109" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>130</v>
       </c>
       <c r="B110" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C110" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>131</v>
       </c>
       <c r="B111" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C111" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>132</v>
       </c>
       <c r="B112" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C112" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>133</v>
       </c>
       <c r="B113" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C113" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>134</v>
       </c>
       <c r="B114" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C114" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>135</v>
       </c>
       <c r="B115" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C115" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>136</v>
       </c>
       <c r="B116" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C116" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>137</v>
       </c>
       <c r="B117" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C117" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>138</v>
       </c>
       <c r="B118" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C118" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>139</v>
       </c>
       <c r="B119" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C119" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>140</v>
       </c>
       <c r="B120" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C120" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>141</v>
       </c>
       <c r="B121" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C121" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>142</v>
       </c>
       <c r="B122" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C122" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>143</v>
       </c>
       <c r="B123" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C123" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>144</v>
       </c>
       <c r="B124" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C124" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>145</v>
       </c>
       <c r="B125" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C125" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>146</v>
       </c>
       <c r="B126" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C126" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>147</v>
       </c>
       <c r="B127" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C127" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>148</v>
       </c>
       <c r="B128" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C128" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>149</v>
       </c>
       <c r="B129" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C129" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>150</v>
       </c>
       <c r="B130" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C130" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>151</v>
       </c>
       <c r="B131" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C131" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>152</v>
       </c>
       <c r="B132" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C132" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>153</v>
       </c>
       <c r="B133" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C133" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>154</v>
       </c>
       <c r="B134" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C134" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>155</v>
       </c>
       <c r="B135" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C135" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>156</v>
       </c>
       <c r="B136" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C136" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>157</v>
       </c>
       <c r="B137" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C137" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>158</v>
       </c>
       <c r="B138" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C138" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>159</v>
       </c>
       <c r="B139" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C139" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>160</v>
       </c>
       <c r="B140" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C140" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>161</v>
       </c>
       <c r="B141" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C141" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>162</v>
       </c>
       <c r="B142" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C142" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>163</v>
       </c>
       <c r="B143" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C143" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>164</v>
       </c>
       <c r="B144" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C144" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>165</v>
       </c>
       <c r="B145" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C145" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>166</v>
       </c>
       <c r="B146" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C146" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>167</v>
       </c>
       <c r="B147" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C147" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>168</v>
       </c>
       <c r="B148" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C148" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>169</v>
       </c>
       <c r="B149" t="s">
         <v>10</v>
       </c>
+      <c r="C149" t="s">
+        <v>173</v>
+      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:C149" xr:uid="{08FC4AC1-13E2-4978-9F20-D861F52E4B90}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/prodotti.xlsx
+++ b/prodotti.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\flashmac\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB410E43-0D82-4C0D-9E91-16557F1D947C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8889C3A-4D30-49BC-B80D-0A9592DEAF30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Attivi" sheetId="1" r:id="rId1"/>
@@ -556,9 +556,6 @@
     <t>Valore protetto new</t>
   </si>
   <si>
-    <t>componente</t>
-  </si>
-  <si>
     <t>PU</t>
   </si>
   <si>
@@ -566,6 +563,9 @@
   </si>
   <si>
     <t>PA + PU</t>
+  </si>
+  <si>
+    <t>componenti</t>
   </si>
 </sst>
 </file>
@@ -899,7 +899,7 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -910,7 +910,7 @@
         <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -921,7 +921,7 @@
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -932,7 +932,7 @@
         <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -943,7 +943,7 @@
         <v>5</v>
       </c>
       <c r="C5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -954,7 +954,7 @@
         <v>3</v>
       </c>
       <c r="C6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -965,7 +965,7 @@
         <v>10</v>
       </c>
       <c r="C7" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -976,7 +976,7 @@
         <v>10</v>
       </c>
       <c r="C8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -987,7 +987,7 @@
         <v>13</v>
       </c>
       <c r="C9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -998,7 +998,7 @@
         <v>3</v>
       </c>
       <c r="C10" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -1009,7 +1009,7 @@
         <v>13</v>
       </c>
       <c r="C11" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -1020,7 +1020,7 @@
         <v>13</v>
       </c>
       <c r="C12" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -1031,7 +1031,7 @@
         <v>13</v>
       </c>
       <c r="C13" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -1042,7 +1042,7 @@
         <v>5</v>
       </c>
       <c r="C14" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -1053,7 +1053,7 @@
         <v>10</v>
       </c>
       <c r="C15" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -1064,7 +1064,7 @@
         <v>5</v>
       </c>
       <c r="C16" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
   </sheetData>
@@ -1090,7 +1090,7 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -1101,7 +1101,7 @@
         <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1112,7 +1112,7 @@
         <v>10</v>
       </c>
       <c r="C3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -1123,7 +1123,7 @@
         <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -1134,7 +1134,7 @@
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -1145,7 +1145,7 @@
         <v>10</v>
       </c>
       <c r="C6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -1156,7 +1156,7 @@
         <v>10</v>
       </c>
       <c r="C7" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -1167,7 +1167,7 @@
         <v>10</v>
       </c>
       <c r="C8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -1178,7 +1178,7 @@
         <v>10</v>
       </c>
       <c r="C9" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -1189,7 +1189,7 @@
         <v>10</v>
       </c>
       <c r="C10" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -1200,7 +1200,7 @@
         <v>10</v>
       </c>
       <c r="C11" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -1211,7 +1211,7 @@
         <v>10</v>
       </c>
       <c r="C12" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -1222,7 +1222,7 @@
         <v>10</v>
       </c>
       <c r="C13" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -1233,7 +1233,7 @@
         <v>10</v>
       </c>
       <c r="C14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -1244,7 +1244,7 @@
         <v>10</v>
       </c>
       <c r="C15" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -1255,7 +1255,7 @@
         <v>10</v>
       </c>
       <c r="C16" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -1266,7 +1266,7 @@
         <v>10</v>
       </c>
       <c r="C17" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -1277,7 +1277,7 @@
         <v>10</v>
       </c>
       <c r="C18" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -1288,7 +1288,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -1299,7 +1299,7 @@
         <v>10</v>
       </c>
       <c r="C20" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -1310,7 +1310,7 @@
         <v>10</v>
       </c>
       <c r="C21" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -1321,7 +1321,7 @@
         <v>10</v>
       </c>
       <c r="C22" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -1332,7 +1332,7 @@
         <v>10</v>
       </c>
       <c r="C23" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -1343,7 +1343,7 @@
         <v>10</v>
       </c>
       <c r="C24" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -1354,7 +1354,7 @@
         <v>10</v>
       </c>
       <c r="C25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -1365,7 +1365,7 @@
         <v>10</v>
       </c>
       <c r="C26" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -1376,7 +1376,7 @@
         <v>10</v>
       </c>
       <c r="C27" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -1387,7 +1387,7 @@
         <v>10</v>
       </c>
       <c r="C28" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -1398,7 +1398,7 @@
         <v>10</v>
       </c>
       <c r="C29" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
@@ -1409,7 +1409,7 @@
         <v>10</v>
       </c>
       <c r="C30" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -1420,7 +1420,7 @@
         <v>10</v>
       </c>
       <c r="C31" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -1431,7 +1431,7 @@
         <v>10</v>
       </c>
       <c r="C32" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
@@ -1442,7 +1442,7 @@
         <v>10</v>
       </c>
       <c r="C33" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
@@ -1453,7 +1453,7 @@
         <v>10</v>
       </c>
       <c r="C34" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
@@ -1464,7 +1464,7 @@
         <v>13</v>
       </c>
       <c r="C35" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
@@ -1475,7 +1475,7 @@
         <v>13</v>
       </c>
       <c r="C36" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
@@ -1486,7 +1486,7 @@
         <v>13</v>
       </c>
       <c r="C37" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
@@ -1497,7 +1497,7 @@
         <v>13</v>
       </c>
       <c r="C38" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
@@ -1508,7 +1508,7 @@
         <v>13</v>
       </c>
       <c r="C39" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
@@ -1519,7 +1519,7 @@
         <v>13</v>
       </c>
       <c r="C40" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
@@ -1530,7 +1530,7 @@
         <v>25</v>
       </c>
       <c r="C41" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
@@ -1541,7 +1541,7 @@
         <v>25</v>
       </c>
       <c r="C42" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
@@ -1552,7 +1552,7 @@
         <v>25</v>
       </c>
       <c r="C43" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
@@ -1563,7 +1563,7 @@
         <v>25</v>
       </c>
       <c r="C44" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
@@ -1574,7 +1574,7 @@
         <v>10</v>
       </c>
       <c r="C45" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
@@ -1585,7 +1585,7 @@
         <v>25</v>
       </c>
       <c r="C46" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
@@ -1596,7 +1596,7 @@
         <v>25</v>
       </c>
       <c r="C47" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
@@ -1607,7 +1607,7 @@
         <v>25</v>
       </c>
       <c r="C48" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
@@ -1618,7 +1618,7 @@
         <v>25</v>
       </c>
       <c r="C49" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
@@ -1629,7 +1629,7 @@
         <v>10</v>
       </c>
       <c r="C50" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
@@ -1640,7 +1640,7 @@
         <v>25</v>
       </c>
       <c r="C51" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
@@ -1651,7 +1651,7 @@
         <v>10</v>
       </c>
       <c r="C52" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
@@ -1662,7 +1662,7 @@
         <v>10</v>
       </c>
       <c r="C53" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
@@ -1673,7 +1673,7 @@
         <v>25</v>
       </c>
       <c r="C54" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
@@ -1684,7 +1684,7 @@
         <v>25</v>
       </c>
       <c r="C55" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
@@ -1695,7 +1695,7 @@
         <v>25</v>
       </c>
       <c r="C56" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
@@ -1706,7 +1706,7 @@
         <v>25</v>
       </c>
       <c r="C57" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
@@ -1717,7 +1717,7 @@
         <v>10</v>
       </c>
       <c r="C58" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
@@ -1728,7 +1728,7 @@
         <v>10</v>
       </c>
       <c r="C59" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
@@ -1739,7 +1739,7 @@
         <v>10</v>
       </c>
       <c r="C60" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
@@ -1750,7 +1750,7 @@
         <v>3</v>
       </c>
       <c r="C61" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
@@ -1761,7 +1761,7 @@
         <v>10</v>
       </c>
       <c r="C62" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
@@ -1772,7 +1772,7 @@
         <v>10</v>
       </c>
       <c r="C63" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
@@ -1783,7 +1783,7 @@
         <v>3</v>
       </c>
       <c r="C64" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
@@ -1794,7 +1794,7 @@
         <v>10</v>
       </c>
       <c r="C65" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
@@ -1805,7 +1805,7 @@
         <v>10</v>
       </c>
       <c r="C66" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
@@ -1816,7 +1816,7 @@
         <v>10</v>
       </c>
       <c r="C67" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
@@ -1827,7 +1827,7 @@
         <v>10</v>
       </c>
       <c r="C68" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
@@ -1838,7 +1838,7 @@
         <v>3</v>
       </c>
       <c r="C69" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
@@ -1849,7 +1849,7 @@
         <v>3</v>
       </c>
       <c r="C70" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
@@ -1860,7 +1860,7 @@
         <v>3</v>
       </c>
       <c r="C71" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
@@ -1871,7 +1871,7 @@
         <v>25</v>
       </c>
       <c r="C72" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
@@ -1882,7 +1882,7 @@
         <v>10</v>
       </c>
       <c r="C73" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
@@ -1893,7 +1893,7 @@
         <v>10</v>
       </c>
       <c r="C74" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
@@ -1904,7 +1904,7 @@
         <v>10</v>
       </c>
       <c r="C75" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
@@ -1915,7 +1915,7 @@
         <v>10</v>
       </c>
       <c r="C76" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
@@ -1926,7 +1926,7 @@
         <v>10</v>
       </c>
       <c r="C77" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
@@ -1937,7 +1937,7 @@
         <v>10</v>
       </c>
       <c r="C78" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
@@ -1948,7 +1948,7 @@
         <v>10</v>
       </c>
       <c r="C79" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
@@ -1959,7 +1959,7 @@
         <v>13</v>
       </c>
       <c r="C80" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
@@ -1970,7 +1970,7 @@
         <v>25</v>
       </c>
       <c r="C81" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
@@ -1981,7 +1981,7 @@
         <v>13</v>
       </c>
       <c r="C82" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
@@ -1992,7 +1992,7 @@
         <v>10</v>
       </c>
       <c r="C83" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
@@ -2003,7 +2003,7 @@
         <v>10</v>
       </c>
       <c r="C84" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
@@ -2014,7 +2014,7 @@
         <v>10</v>
       </c>
       <c r="C85" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
@@ -2025,7 +2025,7 @@
         <v>10</v>
       </c>
       <c r="C86" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
@@ -2036,7 +2036,7 @@
         <v>10</v>
       </c>
       <c r="C87" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
@@ -2047,7 +2047,7 @@
         <v>25</v>
       </c>
       <c r="C88" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
@@ -2058,7 +2058,7 @@
         <v>25</v>
       </c>
       <c r="C89" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
@@ -2069,7 +2069,7 @@
         <v>25</v>
       </c>
       <c r="C90" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
@@ -2080,7 +2080,7 @@
         <v>25</v>
       </c>
       <c r="C91" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
@@ -2091,7 +2091,7 @@
         <v>25</v>
       </c>
       <c r="C92" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
@@ -2102,7 +2102,7 @@
         <v>25</v>
       </c>
       <c r="C93" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
@@ -2113,7 +2113,7 @@
         <v>25</v>
       </c>
       <c r="C94" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
@@ -2124,7 +2124,7 @@
         <v>25</v>
       </c>
       <c r="C95" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
@@ -2135,7 +2135,7 @@
         <v>25</v>
       </c>
       <c r="C96" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
@@ -2146,7 +2146,7 @@
         <v>25</v>
       </c>
       <c r="C97" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
@@ -2157,7 +2157,7 @@
         <v>25</v>
       </c>
       <c r="C98" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
@@ -2168,7 +2168,7 @@
         <v>10</v>
       </c>
       <c r="C99" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
@@ -2179,7 +2179,7 @@
         <v>10</v>
       </c>
       <c r="C100" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
@@ -2190,7 +2190,7 @@
         <v>10</v>
       </c>
       <c r="C101" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
@@ -2201,7 +2201,7 @@
         <v>10</v>
       </c>
       <c r="C102" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
@@ -2212,7 +2212,7 @@
         <v>10</v>
       </c>
       <c r="C103" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
@@ -2223,7 +2223,7 @@
         <v>10</v>
       </c>
       <c r="C104" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
@@ -2234,7 +2234,7 @@
         <v>10</v>
       </c>
       <c r="C105" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
@@ -2245,7 +2245,7 @@
         <v>10</v>
       </c>
       <c r="C106" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
@@ -2256,7 +2256,7 @@
         <v>13</v>
       </c>
       <c r="C107" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
@@ -2267,7 +2267,7 @@
         <v>10</v>
       </c>
       <c r="C108" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
@@ -2278,7 +2278,7 @@
         <v>10</v>
       </c>
       <c r="C109" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
@@ -2289,7 +2289,7 @@
         <v>25</v>
       </c>
       <c r="C110" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
@@ -2300,7 +2300,7 @@
         <v>25</v>
       </c>
       <c r="C111" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
@@ -2311,7 +2311,7 @@
         <v>25</v>
       </c>
       <c r="C112" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
@@ -2322,7 +2322,7 @@
         <v>25</v>
       </c>
       <c r="C113" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
@@ -2333,7 +2333,7 @@
         <v>3</v>
       </c>
       <c r="C114" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
@@ -2344,7 +2344,7 @@
         <v>10</v>
       </c>
       <c r="C115" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
@@ -2355,7 +2355,7 @@
         <v>10</v>
       </c>
       <c r="C116" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
@@ -2366,7 +2366,7 @@
         <v>25</v>
       </c>
       <c r="C117" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
@@ -2377,7 +2377,7 @@
         <v>25</v>
       </c>
       <c r="C118" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
@@ -2388,7 +2388,7 @@
         <v>25</v>
       </c>
       <c r="C119" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
@@ -2399,7 +2399,7 @@
         <v>13</v>
       </c>
       <c r="C120" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
@@ -2410,7 +2410,7 @@
         <v>13</v>
       </c>
       <c r="C121" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
@@ -2421,7 +2421,7 @@
         <v>13</v>
       </c>
       <c r="C122" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
@@ -2432,7 +2432,7 @@
         <v>13</v>
       </c>
       <c r="C123" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
@@ -2443,7 +2443,7 @@
         <v>13</v>
       </c>
       <c r="C124" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
@@ -2454,7 +2454,7 @@
         <v>13</v>
       </c>
       <c r="C125" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
@@ -2465,7 +2465,7 @@
         <v>25</v>
       </c>
       <c r="C126" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.25">
@@ -2476,7 +2476,7 @@
         <v>13</v>
       </c>
       <c r="C127" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
@@ -2487,7 +2487,7 @@
         <v>10</v>
       </c>
       <c r="C128" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
@@ -2498,7 +2498,7 @@
         <v>25</v>
       </c>
       <c r="C129" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
@@ -2509,7 +2509,7 @@
         <v>25</v>
       </c>
       <c r="C130" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
@@ -2520,7 +2520,7 @@
         <v>25</v>
       </c>
       <c r="C131" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
@@ -2531,7 +2531,7 @@
         <v>13</v>
       </c>
       <c r="C132" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.25">
@@ -2542,7 +2542,7 @@
         <v>13</v>
       </c>
       <c r="C133" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
@@ -2553,7 +2553,7 @@
         <v>13</v>
       </c>
       <c r="C134" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
@@ -2564,7 +2564,7 @@
         <v>10</v>
       </c>
       <c r="C135" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.25">
@@ -2575,7 +2575,7 @@
         <v>10</v>
       </c>
       <c r="C136" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.25">
@@ -2586,7 +2586,7 @@
         <v>10</v>
       </c>
       <c r="C137" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.25">
@@ -2597,7 +2597,7 @@
         <v>10</v>
       </c>
       <c r="C138" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
@@ -2608,7 +2608,7 @@
         <v>25</v>
       </c>
       <c r="C139" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
@@ -2619,7 +2619,7 @@
         <v>10</v>
       </c>
       <c r="C140" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
@@ -2630,7 +2630,7 @@
         <v>3</v>
       </c>
       <c r="C141" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
@@ -2641,7 +2641,7 @@
         <v>10</v>
       </c>
       <c r="C142" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
@@ -2652,7 +2652,7 @@
         <v>25</v>
       </c>
       <c r="C143" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
@@ -2663,7 +2663,7 @@
         <v>25</v>
       </c>
       <c r="C144" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
@@ -2674,7 +2674,7 @@
         <v>25</v>
       </c>
       <c r="C145" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
@@ -2685,7 +2685,7 @@
         <v>25</v>
       </c>
       <c r="C146" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
@@ -2696,7 +2696,7 @@
         <v>25</v>
       </c>
       <c r="C147" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
@@ -2707,7 +2707,7 @@
         <v>10</v>
       </c>
       <c r="C148" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
@@ -2718,7 +2718,7 @@
         <v>10</v>
       </c>
       <c r="C149" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
   </sheetData>

--- a/prodotti.xlsx
+++ b/prodotti.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\flashmac\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8889C3A-4D30-49BC-B80D-0A9592DEAF30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B0F6A80-28F1-499C-9F51-3720AEA1A1EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Attivi" sheetId="1" r:id="rId1"/>
@@ -572,13 +572,18 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
     </font>
   </fonts>
   <fills count="2">
@@ -601,9 +606,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -885,24 +891,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C16"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="38" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="2" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -913,7 +919,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -924,7 +930,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -935,7 +941,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -946,7 +952,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -957,7 +963,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -968,7 +974,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -979,7 +985,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -990,7 +996,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -1001,7 +1007,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3">
       <c r="A11" t="s">
         <v>15</v>
       </c>
@@ -1012,7 +1018,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3">
       <c r="A12" t="s">
         <v>16</v>
       </c>
@@ -1023,7 +1029,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3">
       <c r="A13" t="s">
         <v>17</v>
       </c>
@@ -1034,7 +1040,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3">
       <c r="A14" s="1" t="s">
         <v>18</v>
       </c>
@@ -1045,7 +1051,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3">
       <c r="A15" t="s">
         <v>19</v>
       </c>
@@ -1056,7 +1062,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3">
       <c r="A16" t="s">
         <v>20</v>
       </c>
@@ -1076,13 +1082,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08FC4AC1-13E2-4978-9F20-D861F52E4B90}">
   <dimension ref="A1:C149"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1093,7 +1099,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>21</v>
       </c>
@@ -1104,7 +1110,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>22</v>
       </c>
@@ -1115,7 +1121,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>23</v>
       </c>
@@ -1126,7 +1132,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>24</v>
       </c>
@@ -1137,7 +1143,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>26</v>
       </c>
@@ -1148,7 +1154,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>27</v>
       </c>
@@ -1159,7 +1165,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>28</v>
       </c>
@@ -1170,7 +1176,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>29</v>
       </c>
@@ -1181,7 +1187,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3">
       <c r="A10" t="s">
         <v>30</v>
       </c>
@@ -1192,7 +1198,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3">
       <c r="A11" t="s">
         <v>31</v>
       </c>
@@ -1203,7 +1209,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3">
       <c r="A12" t="s">
         <v>32</v>
       </c>
@@ -1214,7 +1220,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3">
       <c r="A13" t="s">
         <v>33</v>
       </c>
@@ -1225,7 +1231,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3">
       <c r="A14" t="s">
         <v>34</v>
       </c>
@@ -1236,7 +1242,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3">
       <c r="A15" t="s">
         <v>35</v>
       </c>
@@ -1247,7 +1253,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3">
       <c r="A16" t="s">
         <v>36</v>
       </c>
@@ -1258,7 +1264,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3">
       <c r="A17" t="s">
         <v>37</v>
       </c>
@@ -1269,7 +1275,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3">
       <c r="A18" t="s">
         <v>38</v>
       </c>
@@ -1280,7 +1286,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3">
       <c r="A19" t="s">
         <v>39</v>
       </c>
@@ -1291,7 +1297,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3">
       <c r="A20" t="s">
         <v>40</v>
       </c>
@@ -1302,7 +1308,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3">
       <c r="A21" t="s">
         <v>41</v>
       </c>
@@ -1313,7 +1319,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3">
       <c r="A22" t="s">
         <v>42</v>
       </c>
@@ -1324,7 +1330,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3">
       <c r="A23" t="s">
         <v>43</v>
       </c>
@@ -1335,7 +1341,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3">
       <c r="A24" t="s">
         <v>44</v>
       </c>
@@ -1346,7 +1352,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3">
       <c r="A25" t="s">
         <v>45</v>
       </c>
@@ -1357,7 +1363,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3">
       <c r="A26" t="s">
         <v>46</v>
       </c>
@@ -1368,7 +1374,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3">
       <c r="A27" t="s">
         <v>47</v>
       </c>
@@ -1379,7 +1385,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3">
       <c r="A28" t="s">
         <v>48</v>
       </c>
@@ -1390,7 +1396,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3">
       <c r="A29" t="s">
         <v>49</v>
       </c>
@@ -1401,7 +1407,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3">
       <c r="A30" t="s">
         <v>50</v>
       </c>
@@ -1412,7 +1418,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3">
       <c r="A31" t="s">
         <v>51</v>
       </c>
@@ -1423,7 +1429,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3">
       <c r="A32" t="s">
         <v>52</v>
       </c>
@@ -1434,7 +1440,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3">
       <c r="A33" t="s">
         <v>53</v>
       </c>
@@ -1445,7 +1451,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3">
       <c r="A34" t="s">
         <v>54</v>
       </c>
@@ -1456,7 +1462,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3">
       <c r="A35" t="s">
         <v>55</v>
       </c>
@@ -1467,7 +1473,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3">
       <c r="A36" t="s">
         <v>56</v>
       </c>
@@ -1478,7 +1484,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3">
       <c r="A37" t="s">
         <v>57</v>
       </c>
@@ -1489,7 +1495,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3">
       <c r="A38" t="s">
         <v>58</v>
       </c>
@@ -1500,7 +1506,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3">
       <c r="A39" t="s">
         <v>59</v>
       </c>
@@ -1511,7 +1517,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3">
       <c r="A40" t="s">
         <v>60</v>
       </c>
@@ -1522,7 +1528,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3">
       <c r="A41" t="s">
         <v>61</v>
       </c>
@@ -1533,7 +1539,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3">
       <c r="A42" t="s">
         <v>62</v>
       </c>
@@ -1544,7 +1550,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3">
       <c r="A43" t="s">
         <v>63</v>
       </c>
@@ -1555,7 +1561,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3">
       <c r="A44" t="s">
         <v>64</v>
       </c>
@@ -1566,7 +1572,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3">
       <c r="A45" t="s">
         <v>65</v>
       </c>
@@ -1577,7 +1583,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3">
       <c r="A46" t="s">
         <v>66</v>
       </c>
@@ -1588,7 +1594,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3">
       <c r="A47" t="s">
         <v>67</v>
       </c>
@@ -1599,7 +1605,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3">
       <c r="A48" t="s">
         <v>68</v>
       </c>
@@ -1610,7 +1616,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3">
       <c r="A49" t="s">
         <v>69</v>
       </c>
@@ -1621,7 +1627,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3">
       <c r="A50" t="s">
         <v>70</v>
       </c>
@@ -1632,7 +1638,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3">
       <c r="A51" t="s">
         <v>71</v>
       </c>
@@ -1643,7 +1649,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3">
       <c r="A52" t="s">
         <v>72</v>
       </c>
@@ -1654,7 +1660,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3">
       <c r="A53" t="s">
         <v>73</v>
       </c>
@@ -1665,7 +1671,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3">
       <c r="A54" t="s">
         <v>74</v>
       </c>
@@ -1676,7 +1682,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3">
       <c r="A55" t="s">
         <v>75</v>
       </c>
@@ -1687,7 +1693,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3">
       <c r="A56" t="s">
         <v>76</v>
       </c>
@@ -1698,7 +1704,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3">
       <c r="A57" t="s">
         <v>77</v>
       </c>
@@ -1709,7 +1715,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3">
       <c r="A58" t="s">
         <v>78</v>
       </c>
@@ -1720,7 +1726,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3">
       <c r="A59" t="s">
         <v>79</v>
       </c>
@@ -1731,7 +1737,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3">
       <c r="A60" t="s">
         <v>80</v>
       </c>
@@ -1742,7 +1748,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3">
       <c r="A61" t="s">
         <v>81</v>
       </c>
@@ -1753,7 +1759,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3">
       <c r="A62" t="s">
         <v>82</v>
       </c>
@@ -1764,7 +1770,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3">
       <c r="A63" t="s">
         <v>83</v>
       </c>
@@ -1775,7 +1781,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3">
       <c r="A64" t="s">
         <v>84</v>
       </c>
@@ -1786,7 +1792,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3">
       <c r="A65" t="s">
         <v>85</v>
       </c>
@@ -1797,7 +1803,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:3">
       <c r="A66" t="s">
         <v>86</v>
       </c>
@@ -1808,7 +1814,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:3">
       <c r="A67" t="s">
         <v>87</v>
       </c>
@@ -1819,7 +1825,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:3">
       <c r="A68" t="s">
         <v>88</v>
       </c>
@@ -1830,7 +1836,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:3">
       <c r="A69" t="s">
         <v>89</v>
       </c>
@@ -1841,7 +1847,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:3">
       <c r="A70" t="s">
         <v>90</v>
       </c>
@@ -1852,7 +1858,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:3">
       <c r="A71" t="s">
         <v>91</v>
       </c>
@@ -1863,7 +1869,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:3">
       <c r="A72" t="s">
         <v>92</v>
       </c>
@@ -1874,7 +1880,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:3">
       <c r="A73" t="s">
         <v>93</v>
       </c>
@@ -1885,7 +1891,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:3">
       <c r="A74" t="s">
         <v>94</v>
       </c>
@@ -1896,7 +1902,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:3">
       <c r="A75" t="s">
         <v>95</v>
       </c>
@@ -1907,7 +1913,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:3">
       <c r="A76" t="s">
         <v>96</v>
       </c>
@@ -1918,7 +1924,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:3">
       <c r="A77" t="s">
         <v>97</v>
       </c>
@@ -1929,7 +1935,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:3">
       <c r="A78" t="s">
         <v>98</v>
       </c>
@@ -1940,7 +1946,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:3">
       <c r="A79" t="s">
         <v>99</v>
       </c>
@@ -1951,7 +1957,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:3">
       <c r="A80" t="s">
         <v>100</v>
       </c>
@@ -1962,7 +1968,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:3">
       <c r="A81" t="s">
         <v>101</v>
       </c>
@@ -1973,7 +1979,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:3">
       <c r="A82" t="s">
         <v>102</v>
       </c>
@@ -1984,7 +1990,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:3">
       <c r="A83" t="s">
         <v>103</v>
       </c>
@@ -1995,7 +2001,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:3">
       <c r="A84" t="s">
         <v>104</v>
       </c>
@@ -2006,7 +2012,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:3">
       <c r="A85" t="s">
         <v>105</v>
       </c>
@@ -2017,7 +2023,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:3">
       <c r="A86" t="s">
         <v>106</v>
       </c>
@@ -2028,7 +2034,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:3">
       <c r="A87" t="s">
         <v>107</v>
       </c>
@@ -2039,7 +2045,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:3">
       <c r="A88" t="s">
         <v>108</v>
       </c>
@@ -2050,7 +2056,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:3">
       <c r="A89" t="s">
         <v>109</v>
       </c>
@@ -2061,7 +2067,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:3">
       <c r="A90" t="s">
         <v>110</v>
       </c>
@@ -2072,7 +2078,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:3">
       <c r="A91" t="s">
         <v>111</v>
       </c>
@@ -2083,7 +2089,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:3">
       <c r="A92" t="s">
         <v>112</v>
       </c>
@@ -2094,7 +2100,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:3">
       <c r="A93" t="s">
         <v>113</v>
       </c>
@@ -2105,7 +2111,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:3">
       <c r="A94" t="s">
         <v>114</v>
       </c>
@@ -2116,7 +2122,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:3">
       <c r="A95" t="s">
         <v>115</v>
       </c>
@@ -2127,7 +2133,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:3">
       <c r="A96" t="s">
         <v>116</v>
       </c>
@@ -2138,7 +2144,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:3">
       <c r="A97" t="s">
         <v>117</v>
       </c>
@@ -2149,7 +2155,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:3">
       <c r="A98" t="s">
         <v>118</v>
       </c>
@@ -2160,7 +2166,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:3">
       <c r="A99" t="s">
         <v>119</v>
       </c>
@@ -2171,7 +2177,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:3">
       <c r="A100" t="s">
         <v>120</v>
       </c>
@@ -2182,7 +2188,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:3">
       <c r="A101" t="s">
         <v>121</v>
       </c>
@@ -2193,7 +2199,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:3">
       <c r="A102" t="s">
         <v>122</v>
       </c>
@@ -2204,7 +2210,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:3">
       <c r="A103" t="s">
         <v>123</v>
       </c>
@@ -2215,7 +2221,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:3">
       <c r="A104" t="s">
         <v>124</v>
       </c>
@@ -2226,7 +2232,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:3">
       <c r="A105" t="s">
         <v>125</v>
       </c>
@@ -2237,7 +2243,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:3">
       <c r="A106" t="s">
         <v>126</v>
       </c>
@@ -2248,7 +2254,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:3">
       <c r="A107" t="s">
         <v>127</v>
       </c>
@@ -2259,7 +2265,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:3">
       <c r="A108" t="s">
         <v>128</v>
       </c>
@@ -2270,7 +2276,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:3">
       <c r="A109" t="s">
         <v>129</v>
       </c>
@@ -2281,7 +2287,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:3">
       <c r="A110" t="s">
         <v>130</v>
       </c>
@@ -2292,7 +2298,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:3">
       <c r="A111" t="s">
         <v>131</v>
       </c>
@@ -2303,7 +2309,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:3">
       <c r="A112" t="s">
         <v>132</v>
       </c>
@@ -2314,7 +2320,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:3">
       <c r="A113" t="s">
         <v>133</v>
       </c>
@@ -2325,7 +2331,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:3">
       <c r="A114" t="s">
         <v>134</v>
       </c>
@@ -2336,7 +2342,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:3">
       <c r="A115" t="s">
         <v>135</v>
       </c>
@@ -2347,7 +2353,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:3">
       <c r="A116" t="s">
         <v>136</v>
       </c>
@@ -2358,7 +2364,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:3">
       <c r="A117" t="s">
         <v>137</v>
       </c>
@@ -2369,7 +2375,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:3">
       <c r="A118" t="s">
         <v>138</v>
       </c>
@@ -2380,7 +2386,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:3">
       <c r="A119" t="s">
         <v>139</v>
       </c>
@@ -2391,7 +2397,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:3">
       <c r="A120" t="s">
         <v>140</v>
       </c>
@@ -2402,7 +2408,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:3">
       <c r="A121" t="s">
         <v>141</v>
       </c>
@@ -2413,7 +2419,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:3">
       <c r="A122" t="s">
         <v>142</v>
       </c>
@@ -2424,7 +2430,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:3">
       <c r="A123" t="s">
         <v>143</v>
       </c>
@@ -2435,7 +2441,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:3">
       <c r="A124" t="s">
         <v>144</v>
       </c>
@@ -2446,7 +2452,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:3">
       <c r="A125" t="s">
         <v>145</v>
       </c>
@@ -2457,7 +2463,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:3">
       <c r="A126" t="s">
         <v>146</v>
       </c>
@@ -2468,7 +2474,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:3">
       <c r="A127" t="s">
         <v>147</v>
       </c>
@@ -2479,7 +2485,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:3">
       <c r="A128" t="s">
         <v>148</v>
       </c>
@@ -2490,7 +2496,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:3">
       <c r="A129" t="s">
         <v>149</v>
       </c>
@@ -2501,7 +2507,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:3">
       <c r="A130" t="s">
         <v>150</v>
       </c>
@@ -2512,7 +2518,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:3">
       <c r="A131" t="s">
         <v>151</v>
       </c>
@@ -2523,7 +2529,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:3">
       <c r="A132" t="s">
         <v>152</v>
       </c>
@@ -2534,7 +2540,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:3">
       <c r="A133" t="s">
         <v>153</v>
       </c>
@@ -2545,7 +2551,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:3">
       <c r="A134" t="s">
         <v>154</v>
       </c>
@@ -2556,7 +2562,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:3">
       <c r="A135" t="s">
         <v>155</v>
       </c>
@@ -2567,7 +2573,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:3">
       <c r="A136" t="s">
         <v>156</v>
       </c>
@@ -2578,7 +2584,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:3">
       <c r="A137" t="s">
         <v>157</v>
       </c>
@@ -2589,7 +2595,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:3">
       <c r="A138" t="s">
         <v>158</v>
       </c>
@@ -2600,7 +2606,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:3">
       <c r="A139" t="s">
         <v>159</v>
       </c>
@@ -2611,7 +2617,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:3">
       <c r="A140" t="s">
         <v>160</v>
       </c>
@@ -2622,7 +2628,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:3">
       <c r="A141" t="s">
         <v>161</v>
       </c>
@@ -2633,7 +2639,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:3">
       <c r="A142" t="s">
         <v>162</v>
       </c>
@@ -2644,7 +2650,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:3">
       <c r="A143" t="s">
         <v>163</v>
       </c>
@@ -2655,7 +2661,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:3">
       <c r="A144" t="s">
         <v>164</v>
       </c>
@@ -2666,7 +2672,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:3">
       <c r="A145" t="s">
         <v>165</v>
       </c>
@@ -2677,7 +2683,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:3">
       <c r="A146" t="s">
         <v>166</v>
       </c>
@@ -2688,7 +2694,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:3">
       <c r="A147" t="s">
         <v>167</v>
       </c>
@@ -2699,7 +2705,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:3">
       <c r="A148" t="s">
         <v>168</v>
       </c>
@@ -2710,7 +2716,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:3">
       <c r="A149" t="s">
         <v>169</v>
       </c>
